--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda - Copia.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842FEF25-AE8D-4EBB-897A-997652279313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2D2A8-ED24-40ED-8F15-9AD92BD88BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>136251253</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -991,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1008,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1028,31 +1031,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>